--- a/week-09/NorthwindTablesAndColumns.xlsx
+++ b/week-09/NorthwindTablesAndColumns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/locelotllopez_my_yearupunited_org/Documents/data analytics/week-09/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{382FC78E-B7F0-4F12-8C72-2E997D4EE2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{2E2BC166-1360-40B1-9F60-2456D768E0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{901F5D27-877F-4C94-89AE-9A9B6ECE5CB6}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="140">
   <si>
     <t>table_name</t>
   </si>
@@ -932,6 +932,9 @@
         <v>92</v>
       </c>
       <c r="K2" s="1"/>
+      <c r="M2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -967,7 +970,7 @@
       <c r="K3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" t="s">
         <v>92</v>
       </c>
     </row>
@@ -996,6 +999,9 @@
       <c r="H4" t="s">
         <v>91</v>
       </c>
+      <c r="M4" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -1022,6 +1028,9 @@
       <c r="H5" t="s">
         <v>91</v>
       </c>
+      <c r="M5" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -1051,6 +1060,9 @@
       <c r="J6" t="s">
         <v>92</v>
       </c>
+      <c r="M6" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -1118,6 +1130,9 @@
       <c r="K8" t="s">
         <v>92</v>
       </c>
+      <c r="M8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
@@ -1150,6 +1165,9 @@
       <c r="K9" t="s">
         <v>92</v>
       </c>
+      <c r="M9" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -1176,6 +1194,9 @@
       <c r="H10" t="s">
         <v>91</v>
       </c>
+      <c r="M10" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
@@ -1281,7 +1302,7 @@
       <c r="K13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1345,6 +1366,9 @@
       <c r="H15" t="s">
         <v>91</v>
       </c>
+      <c r="M15" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
@@ -1371,6 +1395,9 @@
       <c r="H16" t="s">
         <v>91</v>
       </c>
+      <c r="M16" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
@@ -1401,6 +1428,9 @@
         <v>92</v>
       </c>
       <c r="K17" s="1"/>
+      <c r="M17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -1571,7 +1601,7 @@
         <v>92</v>
       </c>
       <c r="K22" s="1"/>
-      <c r="M22" s="1" t="s">
+      <c r="M22" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1607,7 +1637,7 @@
         <v>92</v>
       </c>
       <c r="K23" s="1"/>
-      <c r="M23" s="1" t="s">
+      <c r="M23" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1636,6 +1666,9 @@
       <c r="H24" t="s">
         <v>91</v>
       </c>
+      <c r="M24" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
@@ -1739,7 +1772,7 @@
         <v>92</v>
       </c>
       <c r="K27" s="1"/>
-      <c r="M27" s="1" t="s">
+      <c r="M27" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1803,6 +1836,9 @@
       <c r="H29" t="s">
         <v>91</v>
       </c>
+      <c r="M29" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
@@ -1829,6 +1865,9 @@
       <c r="H30" t="s">
         <v>91</v>
       </c>
+      <c r="M30" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
@@ -1855,6 +1894,9 @@
       <c r="H31" t="s">
         <v>91</v>
       </c>
+      <c r="M31" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
@@ -1881,6 +1923,9 @@
       <c r="H32" t="s">
         <v>91</v>
       </c>
+      <c r="M32" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
@@ -1914,7 +1959,7 @@
         <v>92</v>
       </c>
       <c r="K33" s="1"/>
-      <c r="M33" s="1" t="s">
+      <c r="M33" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1944,6 +1989,9 @@
         <v>91</v>
       </c>
       <c r="I34" s="4"/>
+      <c r="M34" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
@@ -1974,6 +2022,9 @@
       <c r="J35" t="s">
         <v>92</v>
       </c>
+      <c r="M35" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
@@ -2039,6 +2090,9 @@
       <c r="J37" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M37" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
@@ -2212,6 +2266,9 @@
       <c r="J42" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M42" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
@@ -2241,6 +2298,9 @@
       <c r="J43" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M43" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
@@ -2270,6 +2330,9 @@
       <c r="J44" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M44" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
@@ -2302,6 +2365,9 @@
       <c r="J45" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M45" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
@@ -2334,6 +2400,9 @@
       <c r="J46" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M46" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
@@ -2366,6 +2435,9 @@
       <c r="J47" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M47" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
@@ -2398,6 +2470,9 @@
       <c r="J48" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M48" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
@@ -2430,6 +2505,9 @@
       <c r="J49" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M49" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
@@ -2462,7 +2540,7 @@
       <c r="K50" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M50" s="1" t="s">
+      <c r="M50" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2494,6 +2572,9 @@
       <c r="I51" t="s">
         <v>120</v>
       </c>
+      <c r="M51" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
@@ -2526,7 +2607,7 @@
       <c r="K52" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M52" s="1" t="s">
+      <c r="M52" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2561,7 +2642,7 @@
       <c r="K53" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M53" s="1" t="s">
+      <c r="M53" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2596,7 +2677,7 @@
       <c r="J54" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="M54" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2631,7 +2712,7 @@
       <c r="K55" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M55" s="1" t="s">
+      <c r="M55" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2663,6 +2744,9 @@
       <c r="J56" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M56" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
@@ -2695,7 +2779,7 @@
       <c r="K57" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M57" s="1" t="s">
+      <c r="M57" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2727,6 +2811,9 @@
       <c r="J58" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M58" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
@@ -2756,6 +2843,9 @@
       <c r="J59" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M59" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
@@ -2788,7 +2878,7 @@
       <c r="J60" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M60" s="1" t="s">
+      <c r="M60" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2823,7 +2913,7 @@
       <c r="J61" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M61" s="1" t="s">
+      <c r="M61" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2858,7 +2948,7 @@
       <c r="J62" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M62" s="1" t="s">
+      <c r="M62" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2893,7 +2983,7 @@
       <c r="J63" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M63" s="1" t="s">
+      <c r="M63" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2928,7 +3018,7 @@
       <c r="J64" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M64" s="1" t="s">
+      <c r="M64" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2964,6 +3054,9 @@
       <c r="K65" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M65" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
@@ -2993,6 +3086,9 @@
       <c r="J66" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M66" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
@@ -3019,6 +3115,9 @@
       <c r="H67" s="1" t="s">
         <v>91</v>
       </c>
+      <c r="M67" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
@@ -3048,6 +3147,9 @@
       <c r="J68" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M68" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
@@ -3080,7 +3182,7 @@
       <c r="K69" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M69" s="1" t="s">
+      <c r="M69" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3109,6 +3211,9 @@
       <c r="H70" t="s">
         <v>91</v>
       </c>
+      <c r="M70" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
@@ -3138,6 +3243,9 @@
       <c r="J71" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M71" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
@@ -3170,7 +3278,7 @@
       <c r="K72" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M72" s="1" t="s">
+      <c r="M72" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3205,6 +3313,9 @@
       <c r="K73" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M73" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
@@ -3237,6 +3348,9 @@
       <c r="K74" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M74" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
@@ -3266,6 +3380,9 @@
       <c r="K75" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="M75" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
@@ -3298,7 +3415,7 @@
       <c r="K76" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M76" s="1" t="s">
+      <c r="M76" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3333,7 +3450,7 @@
       <c r="K77" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M77" s="1" t="s">
+      <c r="M77" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3368,7 +3485,7 @@
       <c r="J78" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M78" s="1" t="s">
+      <c r="M78" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3403,7 +3520,7 @@
       <c r="K79" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M79" s="1" t="s">
+      <c r="M79" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3432,8 +3549,11 @@
       <c r="H80" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="M80" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>78</v>
       </c>
@@ -3458,8 +3578,11 @@
       <c r="H81" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="M81" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>78</v>
       </c>
@@ -3484,8 +3607,11 @@
       <c r="H82" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="M82" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>80</v>
       </c>
@@ -3513,8 +3639,11 @@
       <c r="J83" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="M83" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>80</v>
       </c>
@@ -3539,8 +3668,11 @@
       <c r="H84" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="M84" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>80</v>
       </c>
@@ -3566,6 +3698,9 @@
         <v>92</v>
       </c>
       <c r="J85" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M85" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3576,6 +3711,34 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <MediaLengthInSeconds xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CA5D0A6329BB324E86983B32928CFC2E" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3d7eac4bce3bbb09c82bd908806be82e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9e0b35a9-e6cb-436b-81d4-4440ba439ca5" xmlns:ns3="ced60a7f-99b1-48d2-b555-34851c8026ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eb51570e5b7cb8bd524bc2df5324d4a3" ns2:_="" ns3:_="">
     <xsd:import namespace="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
@@ -3816,35 +3979,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <MediaLengthInSeconds xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0257D61C-6042-483B-9C34-3DE0D82CB154}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB560F9-4CC1-4243-8F16-7FDC2CD703FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
+    <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA285021-94D7-4152-B2E7-B2D9504C2DBD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3861,23 +4015,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB560F9-4CC1-4243-8F16-7FDC2CD703FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
-    <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0257D61C-6042-483B-9C34-3DE0D82CB154}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/week-09/NorthwindTablesAndColumns.xlsx
+++ b/week-09/NorthwindTablesAndColumns.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/locelotllopez_my_yearupunited_org/Documents/data analytics/week-09/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{2E2BC166-1360-40B1-9F60-2456D768E0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="14_{2E2BC166-1360-40B1-9F60-2456D768E0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61118B5A-403D-40A1-BC3A-1E32C7467B23}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{901F5D27-877F-4C94-89AE-9A9B6ECE5CB6}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{901F5D27-877F-4C94-89AE-9A9B6ECE5CB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Northwind Columns" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="140">
   <si>
     <t>table_name</t>
   </si>
@@ -542,6 +542,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -849,13 +853,13 @@
     <col min="3" max="3" width="17.109375" customWidth="1"/>
     <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.88671875" customWidth="1"/>
-    <col min="9" max="9" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5546875" customWidth="1"/>
-    <col min="13" max="13" width="11.5546875" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.88671875" customWidth="1"/>
+    <col min="10" max="10" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -922,17 +926,20 @@
         <v>92</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="M2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="N2" t="s">
         <v>92</v>
       </c>
     </row>
@@ -953,24 +960,27 @@
         <v>30</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N3" t="s">
         <v>92</v>
       </c>
     </row>
@@ -990,16 +1000,25 @@
       <c r="E4" s="1">
         <v>16</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>91</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H4" t="s">
-        <v>91</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="H4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I4" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N4" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1019,16 +1038,25 @@
       <c r="E5" s="1">
         <v>16</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>91</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H5" t="s">
-        <v>91</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="H5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N5" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1048,19 +1076,25 @@
       <c r="E6" s="2">
         <v>10</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J6" t="s">
-        <v>92</v>
-      </c>
-      <c r="M6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K6" t="s">
+        <v>92</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N6" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1080,22 +1114,28 @@
       <c r="E7" s="2">
         <v>80</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>91</v>
+      <c r="F7" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>92</v>
+      <c r="H7" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="K7" t="s">
-        <v>92</v>
-      </c>
-      <c r="M7" t="s">
+      <c r="K7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L7" t="s">
+        <v>92</v>
+      </c>
+      <c r="N7" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1115,22 +1155,28 @@
       <c r="E8" s="2">
         <v>60</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>91</v>
+      <c r="F8" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>92</v>
+      <c r="H8" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K8" t="s">
-        <v>92</v>
-      </c>
-      <c r="M8" t="s">
+      <c r="K8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L8" t="s">
+        <v>92</v>
+      </c>
+      <c r="N8" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1150,22 +1196,28 @@
       <c r="E9" s="2">
         <v>60</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>91</v>
+      <c r="F9" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>92</v>
+      <c r="H9" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K9" t="s">
-        <v>92</v>
-      </c>
-      <c r="M9" t="s">
+      <c r="K9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" t="s">
+        <v>92</v>
+      </c>
+      <c r="N9" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1185,16 +1237,22 @@
       <c r="E10" s="2">
         <v>120</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>91</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H10" t="s">
-        <v>91</v>
-      </c>
-      <c r="M10" t="s">
+      <c r="H10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" t="s">
+        <v>91</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N10" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1214,22 +1272,28 @@
       <c r="E11" s="2">
         <v>30</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>91</v>
+      <c r="F11" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>92</v>
+      <c r="H11" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="K11" t="s">
-        <v>92</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="K11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L11" t="s">
+        <v>92</v>
+      </c>
+      <c r="N11" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1249,22 +1313,28 @@
       <c r="E12" s="2">
         <v>30</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>91</v>
+      <c r="F12" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>92</v>
+      <c r="H12" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="K12" t="s">
-        <v>92</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="K12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L12" t="s">
+        <v>92</v>
+      </c>
+      <c r="N12" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1284,25 +1354,28 @@
       <c r="E13" s="2">
         <v>20</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>91</v>
+      <c r="F13" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>92</v>
+      <c r="H13" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="I13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="K13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M13" t="s">
+      <c r="L13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N13" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1322,22 +1395,28 @@
       <c r="E14" s="2">
         <v>30</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>91</v>
+      <c r="F14" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>92</v>
+      <c r="H14" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="I14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="K14" t="s">
-        <v>92</v>
-      </c>
-      <c r="M14" t="s">
+      <c r="K14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L14" t="s">
+        <v>92</v>
+      </c>
+      <c r="N14" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1357,16 +1436,25 @@
       <c r="E15" s="2">
         <v>48</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>91</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H15" t="s">
-        <v>91</v>
-      </c>
-      <c r="M15" t="s">
+      <c r="H15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N15" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1386,20 +1474,29 @@
       <c r="E16" s="2">
         <v>48</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>91</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H16" t="s">
-        <v>91</v>
-      </c>
-      <c r="M16" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" t="s">
+        <v>91</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>27</v>
       </c>
@@ -1415,24 +1512,27 @@
       <c r="E17" s="1">
         <v>4</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K17" s="1"/>
-      <c r="M17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L17" s="1"/>
+      <c r="N17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -1448,26 +1548,32 @@
       <c r="E18" s="1">
         <v>40</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>91</v>
+      <c r="F18" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I18" s="1" t="s">
+      <c r="H18" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>97</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M18" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -1483,26 +1589,32 @@
       <c r="E19" s="1">
         <v>20</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>91</v>
+      <c r="F19" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I19" s="1" t="s">
+      <c r="H19" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>98</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -1518,26 +1630,32 @@
       <c r="E20" s="1">
         <v>60</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>91</v>
+      <c r="F20" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I20" s="1" t="s">
+      <c r="H20" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>103</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M20" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -1553,23 +1671,29 @@
       <c r="E21" s="1">
         <v>50</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="2" t="s">
         <v>91</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>91</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>27</v>
       </c>
@@ -1585,27 +1709,30 @@
       <c r="E22" s="1">
         <v>8</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>91</v>
+      <c r="F22" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I22" s="1" t="s">
+      <c r="H22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K22" s="1"/>
-      <c r="M22" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L22" s="1"/>
+      <c r="N22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
@@ -1621,27 +1748,30 @@
       <c r="E23" s="1">
         <v>8</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>91</v>
+      <c r="F23" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I23" s="1" t="s">
+      <c r="H23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K23" s="1"/>
-      <c r="M23" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K23" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L23" s="1"/>
+      <c r="N23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -1657,20 +1787,29 @@
       <c r="E24" s="1">
         <v>120</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" t="s">
         <v>91</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H24" t="s">
-        <v>91</v>
-      </c>
-      <c r="M24" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
@@ -1686,26 +1825,32 @@
       <c r="E25" s="1">
         <v>30</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>91</v>
+      <c r="F25" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I25" s="1" t="s">
+      <c r="H25" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>99</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M25" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N25" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -1721,26 +1866,32 @@
       <c r="E26" s="1">
         <v>30</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>91</v>
+      <c r="F26" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I26" s="1" t="s">
+      <c r="H26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>106</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M26" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>27</v>
       </c>
@@ -1756,27 +1907,30 @@
       <c r="E27" s="1">
         <v>20</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>91</v>
+      <c r="F27" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I27" s="1" t="s">
+      <c r="H27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K27" s="1"/>
-      <c r="M27" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K27" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L27" s="1"/>
+      <c r="N27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -1792,26 +1946,32 @@
       <c r="E28" s="1">
         <v>30</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>91</v>
+      <c r="F28" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I28" s="4" t="s">
+      <c r="H28" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J28" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="K28" t="s">
-        <v>92</v>
-      </c>
-      <c r="M28" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K28" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L28" t="s">
+        <v>92</v>
+      </c>
+      <c r="N28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -1827,20 +1987,29 @@
       <c r="E29" s="1">
         <v>48</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" t="s">
         <v>91</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H29" t="s">
-        <v>91</v>
-      </c>
-      <c r="M29" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I29" t="s">
+        <v>91</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N29" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>27</v>
       </c>
@@ -1856,20 +2025,29 @@
       <c r="E30" s="1">
         <v>8</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" t="s">
         <v>91</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H30" t="s">
-        <v>91</v>
-      </c>
-      <c r="M30" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I30" t="s">
+        <v>91</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>27</v>
       </c>
@@ -1885,20 +2063,29 @@
       <c r="E31" s="1">
         <v>16</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" t="s">
         <v>91</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H31" t="s">
-        <v>91</v>
-      </c>
-      <c r="M31" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I31" t="s">
+        <v>91</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1914,20 +2101,29 @@
       <c r="E32" s="1">
         <v>16</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" t="s">
         <v>91</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H32" t="s">
-        <v>91</v>
-      </c>
-      <c r="M32" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H32" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I32" t="s">
+        <v>91</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>27</v>
       </c>
@@ -1944,26 +2140,29 @@
         <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I33" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J33" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K33" s="1"/>
-      <c r="M33" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K33" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L33" s="1"/>
+      <c r="N33" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>27</v>
       </c>
@@ -1979,21 +2178,27 @@
       <c r="E34" s="1">
         <v>510</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" t="s">
         <v>91</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H34" t="s">
-        <v>91</v>
-      </c>
-      <c r="I34" s="4"/>
-      <c r="M34" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H34" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I34" t="s">
+        <v>91</v>
+      </c>
+      <c r="J34" s="4"/>
+      <c r="L34" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N34" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>42</v>
       </c>
@@ -2009,24 +2214,30 @@
       <c r="E35" s="2">
         <v>4</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>91</v>
+      <c r="F35" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I35" s="4"/>
-      <c r="J35" t="s">
-        <v>92</v>
-      </c>
-      <c r="M35" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J35" s="4"/>
+      <c r="K35" t="s">
+        <v>92</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>42</v>
       </c>
@@ -2042,26 +2253,32 @@
       <c r="E36" s="2">
         <v>40</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>91</v>
+      <c r="F36" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I36" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J36" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="J36" t="s">
-        <v>92</v>
-      </c>
-      <c r="M36" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K36" t="s">
+        <v>92</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>44</v>
       </c>
@@ -2081,20 +2298,26 @@
         <v>92</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I37" s="4"/>
-      <c r="J37" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M37" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J37" s="4"/>
+      <c r="K37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N37" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
@@ -2111,23 +2334,29 @@
         <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I38" s="4"/>
-      <c r="J38" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M38" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I38" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J38" s="4"/>
+      <c r="K38" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>44</v>
       </c>
@@ -2144,28 +2373,34 @@
         <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I39" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J39" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="K39" s="1" t="s">
         <v>92</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M39" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>44</v>
       </c>
@@ -2182,25 +2417,31 @@
         <v>2</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I40" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J40" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M40" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N40" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>44</v>
       </c>
@@ -2217,28 +2458,34 @@
         <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I41" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J41" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="K41" s="1" t="s">
         <v>92</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M41" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>53</v>
       </c>
@@ -2258,19 +2505,25 @@
         <v>92</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M42" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N42" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>53</v>
       </c>
@@ -2287,22 +2540,28 @@
         <v>10</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M43" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I43" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>53</v>
       </c>
@@ -2319,22 +2578,28 @@
         <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M44" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I44" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N44" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>53</v>
       </c>
@@ -2351,25 +2616,31 @@
         <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I45" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J45" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K45" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>53</v>
       </c>
@@ -2386,25 +2657,31 @@
         <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I46" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J46" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M46" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K46" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N46" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>53</v>
       </c>
@@ -2421,25 +2698,31 @@
         <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J47" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M47" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N47" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>53</v>
       </c>
@@ -2456,25 +2739,31 @@
         <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>92</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M48" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K48" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N48" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>53</v>
       </c>
@@ -2491,25 +2780,31 @@
         <v>8</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I49" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M49" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K49" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N49" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>53</v>
       </c>
@@ -2526,25 +2821,31 @@
         <v>80</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I50" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>119</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M50" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N50" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>53</v>
       </c>
@@ -2560,23 +2861,32 @@
       <c r="E51" s="2">
         <v>120</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" t="s">
         <v>91</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H51" s="1" t="s">
         <v>91</v>
       </c>
       <c r="I51" t="s">
+        <v>91</v>
+      </c>
+      <c r="J51" t="s">
         <v>120</v>
       </c>
-      <c r="M51" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K51" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N51" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>53</v>
       </c>
@@ -2593,25 +2903,31 @@
         <v>30</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>121</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N52" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>53</v>
       </c>
@@ -2628,25 +2944,31 @@
         <v>30</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I53" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J53" s="1" t="s">
         <v>122</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M53" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N53" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>53</v>
       </c>
@@ -2663,25 +2985,31 @@
         <v>20</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I54" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M54" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K54" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N54" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>53</v>
       </c>
@@ -2698,25 +3026,31 @@
         <v>30</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I55" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>123</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M55" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N55" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>65</v>
       </c>
@@ -2736,19 +3070,25 @@
         <v>92</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M56" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N56" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>65</v>
       </c>
@@ -2765,25 +3105,31 @@
         <v>80</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I57" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>125</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M57" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N57" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>65</v>
       </c>
@@ -2800,22 +3146,25 @@
         <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M58" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I58" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N58" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>65</v>
       </c>
@@ -2832,22 +3181,25 @@
         <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M59" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I59" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N59" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>65</v>
       </c>
@@ -2864,25 +3216,28 @@
         <v>40</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I60" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J60" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M60" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K60" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N60" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>65</v>
       </c>
@@ -2899,25 +3254,28 @@
         <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I61" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J61" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M61" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K61" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N61" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>65</v>
       </c>
@@ -2934,25 +3292,28 @@
         <v>2</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I62" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M62" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K62" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N62" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>65</v>
       </c>
@@ -2969,25 +3330,28 @@
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I63" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J63" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M63" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K63" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N63" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>65</v>
       </c>
@@ -3004,25 +3368,28 @@
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I64" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J64" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J64" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M64" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K64" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N64" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>65</v>
       </c>
@@ -3039,26 +3406,29 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I65" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J65" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M65" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K65" s="1"/>
+      <c r="L65" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N65" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>22</v>
       </c>
@@ -3078,19 +3448,22 @@
         <v>92</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M66" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N66" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>22</v>
       </c>
@@ -3115,11 +3488,14 @@
       <c r="H67" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="M67" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I67" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N67" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>76</v>
       </c>
@@ -3139,19 +3515,22 @@
         <v>92</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M68" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N68" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>76</v>
       </c>
@@ -3168,25 +3547,28 @@
         <v>80</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I69" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J69" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="K69" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M69" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L69" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N69" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>76</v>
       </c>
@@ -3202,20 +3584,23 @@
       <c r="E70" s="1">
         <v>48</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" t="s">
         <v>91</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H70" t="s">
-        <v>91</v>
-      </c>
-      <c r="M70" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H70" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I70" t="s">
+        <v>91</v>
+      </c>
+      <c r="N70" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>78</v>
       </c>
@@ -3235,19 +3620,22 @@
         <v>92</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M71" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N71" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>78</v>
       </c>
@@ -3264,25 +3652,28 @@
         <v>80</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I72" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J72" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="K72" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M72" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L72" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N72" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>78</v>
       </c>
@@ -3299,25 +3690,28 @@
         <v>60</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I73" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J73" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="K73" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M73" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L73" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N73" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>78</v>
       </c>
@@ -3334,25 +3728,28 @@
         <v>60</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I74" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J74" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="K74" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M74" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L74" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N74" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>78</v>
       </c>
@@ -3368,23 +3765,26 @@
       <c r="E75" s="2">
         <v>120</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" t="s">
         <v>91</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H75" t="s">
-        <v>91</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M75" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H75" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I75" t="s">
+        <v>91</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N75" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>78</v>
       </c>
@@ -3401,25 +3801,28 @@
         <v>30</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I76" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="K76" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M76" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L76" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N76" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>78</v>
       </c>
@@ -3436,25 +3839,28 @@
         <v>30</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I77" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J77" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="K77" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M77" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L77" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N77" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>78</v>
       </c>
@@ -3471,25 +3877,28 @@
         <v>20</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I78" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J78" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="J78" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M78" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K78" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N78" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>78</v>
       </c>
@@ -3506,25 +3915,28 @@
         <v>30</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>91</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I79" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J79" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="K79" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M79" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L79" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N79" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>78</v>
       </c>
@@ -3540,20 +3952,23 @@
       <c r="E80" s="2">
         <v>48</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F80" t="s">
         <v>91</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H80" t="s">
-        <v>91</v>
-      </c>
-      <c r="M80" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H80" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I80" t="s">
+        <v>91</v>
+      </c>
+      <c r="N80" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>78</v>
       </c>
@@ -3569,20 +3984,23 @@
       <c r="E81" s="2">
         <v>48</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F81" t="s">
         <v>91</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H81" t="s">
-        <v>91</v>
-      </c>
-      <c r="M81" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H81" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I81" t="s">
+        <v>91</v>
+      </c>
+      <c r="N81" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>78</v>
       </c>
@@ -3598,20 +4016,23 @@
       <c r="E82" s="2">
         <v>16</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F82" t="s">
         <v>91</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H82" t="s">
-        <v>91</v>
-      </c>
-      <c r="M82" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H82" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I82" t="s">
+        <v>91</v>
+      </c>
+      <c r="N82" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>80</v>
       </c>
@@ -3631,19 +4052,22 @@
         <v>92</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M83" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N83" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>80</v>
       </c>
@@ -3659,20 +4083,23 @@
       <c r="E84" s="1">
         <v>100</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="F84" t="s">
         <v>91</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H84" t="s">
-        <v>91</v>
-      </c>
-      <c r="M84" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H84" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I84" t="s">
+        <v>91</v>
+      </c>
+      <c r="N84" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>80</v>
       </c>
@@ -3689,18 +4116,21 @@
         <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="J85" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M85" t="s">
+      <c r="I85" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N85" t="s">
         <v>92</v>
       </c>
     </row>
